--- a/题库/Python理论练习题1.xlsx
+++ b/题库/Python理论练习题1.xlsx
@@ -165,33 +165,33 @@
     <t>函数只能返回一个值</t>
   </si>
   <si>
+    <t>下列语句中在 Python 中非法的是（）。</t>
+  </si>
+  <si>
+    <t>x+=y</t>
+  </si>
+  <si>
+    <t>x=(y=z+1)</t>
+  </si>
+  <si>
+    <t>x,y=y,x</t>
+  </si>
+  <si>
+    <t>x=y=z=1</t>
+  </si>
+  <si>
+    <t>下列程序的输出结果是（）。try: x=1/2 except ZeroDivisionError: print ('AAA')</t>
+  </si>
+  <si>
+    <t>无输出</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
-    <t>下列语句中在 Python 中非法的是（）。</t>
-  </si>
-  <si>
-    <t>x+=y</t>
-  </si>
-  <si>
-    <t>x=(y=z+1)</t>
-  </si>
-  <si>
-    <t>x,y=y,x</t>
-  </si>
-  <si>
-    <t>x=y=z=1</t>
-  </si>
-  <si>
-    <t>下列程序的输出结果是（）。try: x=1/2 except ZeroDivisionError: print ('AAA')</t>
-  </si>
-  <si>
-    <t>无输出</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
     <t>关于 Python 语言的注释，以下选项中描述错误的是</t>
   </si>
   <si>
@@ -360,7 +360,7 @@
     <t>表达式 "Hello world !"[-4] 的值为【1】。</t>
   </si>
   <si>
-    <t>'l'</t>
+    <t>r</t>
   </si>
   <si>
     <t>已知 x='hello world.'，那么表达式 x.find ('x') 和 x.rfind ('x') 的值都为【1】。</t>
@@ -1679,7 +1679,7 @@
         <v>43</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I8" s="3">
         <v>2</v>
@@ -1694,22 +1694,22 @@
         <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="H9" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I9" s="3">
         <v>2</v>
@@ -1724,22 +1724,22 @@
         <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E10" s="3">
         <v>0.5</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="I10" s="3">
         <v>2</v>
@@ -1799,7 +1799,7 @@
         <v>62</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I12" s="3">
         <v>2</v>
@@ -1859,7 +1859,7 @@
         <v>72</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I14" s="3">
         <v>2</v>
@@ -1889,7 +1889,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I15" s="3">
         <v>2</v>
@@ -1919,7 +1919,7 @@
         <v>78</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="I16" s="3">
         <v>2</v>
@@ -1949,7 +1949,7 @@
         <v>83</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I17" s="3">
         <v>2</v>
@@ -1979,7 +1979,7 @@
         <v>88</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I18" s="3">
         <v>2</v>
@@ -2009,7 +2009,7 @@
         <v>93</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I19" s="3">
         <v>2</v>
@@ -2039,7 +2039,7 @@
         <v>98</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I20" s="3">
         <v>2</v>
@@ -2099,7 +2099,7 @@
         <v>4112</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I22" s="3">
         <v>2</v>
@@ -2365,7 +2365,7 @@
         <v>124</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>22</v>
@@ -2391,7 +2391,7 @@
         <v>125</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>22</v>
@@ -2417,7 +2417,7 @@
         <v>126</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>22</v>
@@ -2443,7 +2443,7 @@
         <v>127</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>22</v>
@@ -2451,7 +2451,7 @@
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I38" s="5">
         <v>10</v>
@@ -2469,7 +2469,7 @@
         <v>128</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>22</v>
@@ -2477,7 +2477,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I39" s="5">
         <v>10</v>
@@ -2495,7 +2495,7 @@
         <v>129</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>22</v>
@@ -2503,7 +2503,7 @@
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I40" s="5">
         <v>10</v>
@@ -2521,7 +2521,7 @@
         <v>130</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>22</v>
@@ -2529,7 +2529,7 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I41" s="5">
         <v>10</v>
@@ -2547,7 +2547,7 @@
         <v>131</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>22</v>
@@ -2555,7 +2555,7 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I42" s="5">
         <v>10</v>
@@ -2573,7 +2573,7 @@
         <v>132</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>22</v>
@@ -2581,7 +2581,7 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I43" s="5">
         <v>10</v>
@@ -2599,7 +2599,7 @@
         <v>133</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>22</v>
@@ -2607,7 +2607,7 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I44" s="5">
         <v>10</v>
